--- a/elementary_school_project/media/students.xlsx
+++ b/elementary_school_project/media/students.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>20021113</t>
@@ -481,6 +480,112 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20021117</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>a601021061</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20021115</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>a601021071</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20021117</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>a601021061</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20021117</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>a601021061</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20021116</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>a601021061</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20021117</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>a601021071</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20021117</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>a601021061</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>2024</v>
       </c>
     </row>
